--- a/ABVX.xlsx
+++ b/ABVX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F80BD2C-78B1-4F6E-863D-DD4DE98FFBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45720" yWindow="4800" windowWidth="24000" windowHeight="15320" xr2:uid="{8BAA6E96-53E2-47A8-B392-B3025814CD1D}"/>
+    <workbookView xWindow="8980" yWindow="4440" windowWidth="21060" windowHeight="13820" xr2:uid="{8BAA6E96-53E2-47A8-B392-B3025814CD1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -788,16 +788,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5582F7E9-E7AD-459C-ABE3-152BF08D3904}">
   <dimension ref="B2:N7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4"/>
-    <col min="2" max="2" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="12" width="9.140625" style="4"/>
+    <col min="1" max="1" width="9.1796875" style="4"/>
+    <col min="2" max="2" width="11.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="12" width="9.1796875" style="4"/>
     <col min="13" max="13" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="4"/>
+    <col min="14" max="16384" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
@@ -808,7 +808,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
@@ -825,7 +825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="L4" s="4" t="s">
         <v>2</v>
       </c>
@@ -834,7 +834,7 @@
         <v>6334.7837</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="L5" s="4" t="s">
         <v>15</v>
       </c>
@@ -845,7 +845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="L6" s="4" t="s">
         <v>16</v>
       </c>
@@ -857,7 +857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="L7" s="4" t="s">
         <v>17</v>
       </c>
@@ -874,23 +874,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43741EC6-85F5-44A4-B95A-FF645D996B10}">
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="4"/>
-    <col min="5" max="15" width="8.85546875" style="4" customWidth="1"/>
-    <col min="16" max="20" width="9.140625" style="4"/>
-    <col min="21" max="21" width="11.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="4"/>
+    <col min="3" max="4" width="9.1796875" style="4"/>
+    <col min="5" max="15" width="8.81640625" style="4" customWidth="1"/>
+    <col min="16" max="20" width="9.1796875" style="4"/>
+    <col min="21" max="21" width="11.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C2" s="4">
         <v>2025</v>
       </c>
@@ -991,7 +991,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>11718</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>5971</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" s="6" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>914000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>38</v>
       </c>
@@ -1124,22 +1124,22 @@
         <v>6528.5714285714284</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>24</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>26</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>27</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>620.800762181712</v>
       </c>
     </row>
-    <row r="17" spans="2:21" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>320.800762181712</v>
       </c>
     </row>
-    <row r="18" spans="2:21" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>31</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>64.160152436342401</v>
       </c>
     </row>
-    <row r="19" spans="2:21" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
@@ -1650,17 +1650,17 @@
         <v>256.6406097453696</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>34</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="T24" s="4" t="s">
         <v>36</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>10057.669504886186</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
         <v>15</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>158.76894904692935</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="T26" s="4" t="s">
         <v>37</v>
       </c>
@@ -1815,24 +1815,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A116839-BC77-4548-BA51-3104AA1774E3}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>8</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>9</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>10</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -1864,17 +1864,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C7" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C8" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>39</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C15" s="14" t="s">
         <v>42</v>
       </c>
